--- a/MicrosoftErgonomicKeyboardTemplate.xlsx
+++ b/MicrosoftErgonomicKeyboardTemplate.xlsx
@@ -72,7 +72,7 @@
     <t>GitHub</t>
   </si>
   <si>
-    <t>Dev</t>
+    <t>Avanti</t>
   </si>
 </sst>
 </file>
@@ -384,7 +384,7 @@
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E81275FA-B807-45D0-95BA-B3028F00F66E}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E81275FA-B807-45D0-95BA-B3028F00F66E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -445,7 +445,7 @@
         <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{67DADC1F-4FCE-4127-8ABC-DDE558106780}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67DADC1F-4FCE-4127-8ABC-DDE558106780}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -489,7 +489,7 @@
         <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0C7B0966-8AC7-4D01-895A-848816EBEC1C}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C7B0966-8AC7-4D01-895A-848816EBEC1C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -517,14 +517,14 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>19049</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>24490</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>114298</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>563044</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>568485</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>482435</xdr:rowOff>
     </xdr:to>
@@ -533,7 +533,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6A80ACB3-109F-4E48-A35B-61BB3A3E0534}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A80ACB3-109F-4E48-A35B-61BB3A3E0534}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -549,7 +549,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1181841" y="666006"/>
+          <a:off x="606876" y="669469"/>
           <a:ext cx="543995" cy="368137"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -561,8 +561,8 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>1</xdr:col>
-      <xdr:colOff>92032</xdr:colOff>
+      <xdr:col>2</xdr:col>
+      <xdr:colOff>81148</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>83622</xdr:rowOff>
     </xdr:from>
@@ -572,7 +572,7 @@
         <xdr:cNvPr id="11" name="Picture 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{65186B20-B5C5-45B0-BB97-F93092742A0B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65186B20-B5C5-45B0-BB97-F93092742A0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -588,7 +588,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="673428" y="635330"/>
+          <a:off x="1245919" y="638793"/>
           <a:ext cx="409575" cy="493610"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -611,7 +611,7 @@
         <xdr:cNvPr id="13" name="Picture 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{65186B20-B5C5-45B0-BB97-F93092742A0B}"/>
+              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65186B20-B5C5-45B0-BB97-F93092742A0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -830,15 +830,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>8</xdr:col>
-      <xdr:colOff>21771</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>108858</xdr:rowOff>
+      <xdr:colOff>103414</xdr:colOff>
+      <xdr:row>25</xdr:row>
+      <xdr:rowOff>130628</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>8</xdr:col>
-      <xdr:colOff>560614</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>647701</xdr:rowOff>
+      <xdr:col>9</xdr:col>
+      <xdr:colOff>59871</xdr:colOff>
+      <xdr:row>28</xdr:row>
+      <xdr:rowOff>97971</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -855,8 +855,46 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="5078185" y="664029"/>
+          <a:off x="5159828" y="5627914"/>
           <a:ext cx="538843" cy="538843"/>
+        </a:xfrm>
+        <a:prstGeom prst="rect">
+          <a:avLst/>
+        </a:prstGeom>
+      </xdr:spPr>
+    </xdr:pic>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+  <xdr:twoCellAnchor editAs="oneCell">
+    <xdr:from>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>152398</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>168728</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>8</xdr:col>
+      <xdr:colOff>438188</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>530729</xdr:rowOff>
+    </xdr:to>
+    <xdr:pic>
+      <xdr:nvPicPr>
+        <xdr:cNvPr id="16" name="Picture 15"/>
+        <xdr:cNvPicPr>
+          <a:picLocks noChangeAspect="1"/>
+        </xdr:cNvPicPr>
+      </xdr:nvPicPr>
+      <xdr:blipFill>
+        <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId12"/>
+        <a:stretch>
+          <a:fillRect/>
+        </a:stretch>
+      </xdr:blipFill>
+      <xdr:spPr>
+        <a:xfrm>
+          <a:off x="5208812" y="723899"/>
+          <a:ext cx="285790" cy="362001"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1206,10 +1244,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>3</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>4</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>3</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="6" t="s">

--- a/MicrosoftErgonomicKeyboardTemplate.xlsx
+++ b/MicrosoftErgonomicKeyboardTemplate.xlsx
@@ -369,22 +369,22 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>19050</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>104775</xdr:rowOff>
+      <xdr:colOff>54686</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>130628</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>10</xdr:col>
-      <xdr:colOff>561975</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>657225</xdr:rowOff>
+      <xdr:colOff>534760</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>619124</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Picture 1">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{E81275FA-B807-45D0-95BA-B3028F00F66E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{E81275FA-B807-45D0-95BA-B3028F00F66E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -407,8 +407,8 @@
       </xdr:blipFill>
       <xdr:spPr bwMode="auto">
         <a:xfrm>
-          <a:off x="6257925" y="657225"/>
-          <a:ext cx="542925" cy="552450"/>
+          <a:off x="6275872" y="685799"/>
+          <a:ext cx="480074" cy="488496"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -445,7 +445,7 @@
         <xdr:cNvPr id="5" name="Picture 4">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{67DADC1F-4FCE-4127-8ABC-DDE558106780}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{67DADC1F-4FCE-4127-8ABC-DDE558106780}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -489,7 +489,7 @@
         <xdr:cNvPr id="6" name="Picture 5">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0C7B0966-8AC7-4D01-895A-848816EBEC1C}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{0C7B0966-8AC7-4D01-895A-848816EBEC1C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -517,13 +517,13 @@
   </xdr:twoCellAnchor>
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>24490</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>114298</xdr:rowOff>
     </xdr:from>
     <xdr:to>
-      <xdr:col>1</xdr:col>
+      <xdr:col>2</xdr:col>
       <xdr:colOff>568485</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>482435</xdr:rowOff>
@@ -533,7 +533,7 @@
         <xdr:cNvPr id="7" name="Picture 6">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A80ACB3-109F-4E48-A35B-61BB3A3E0534}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{6A80ACB3-109F-4E48-A35B-61BB3A3E0534}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -549,7 +549,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="606876" y="669469"/>
+          <a:off x="1189261" y="669469"/>
           <a:ext cx="543995" cy="368137"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -561,8 +561,8 @@
   </xdr:twoCellAnchor>
   <xdr:oneCellAnchor>
     <xdr:from>
-      <xdr:col>2</xdr:col>
-      <xdr:colOff>81148</xdr:colOff>
+      <xdr:col>1</xdr:col>
+      <xdr:colOff>97475</xdr:colOff>
       <xdr:row>2</xdr:row>
       <xdr:rowOff>83622</xdr:rowOff>
     </xdr:from>
@@ -572,7 +572,7 @@
         <xdr:cNvPr id="11" name="Picture 10">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65186B20-B5C5-45B0-BB97-F93092742A0B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{65186B20-B5C5-45B0-BB97-F93092742A0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -588,7 +588,7 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="1245919" y="638793"/>
+          <a:off x="679861" y="638793"/>
           <a:ext cx="409575" cy="493610"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
@@ -611,7 +611,7 @@
         <xdr:cNvPr id="13" name="Picture 12">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{65186B20-B5C5-45B0-BB97-F93092742A0B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" xmlns="" id="{65186B20-B5C5-45B0-BB97-F93092742A0B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -640,15 +640,15 @@
   <xdr:twoCellAnchor editAs="oneCell">
     <xdr:from>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>66675</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>82663</xdr:rowOff>
+      <xdr:colOff>121104</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>126207</xdr:rowOff>
     </xdr:from>
     <xdr:to>
       <xdr:col>7</xdr:col>
-      <xdr:colOff>533400</xdr:colOff>
-      <xdr:row>2</xdr:row>
-      <xdr:rowOff>653568</xdr:rowOff>
+      <xdr:colOff>489857</xdr:colOff>
+      <xdr:row>2</xdr:row>
+      <xdr:rowOff>577271</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
@@ -665,8 +665,8 @@
       </xdr:blipFill>
       <xdr:spPr>
         <a:xfrm>
-          <a:off x="4533900" y="635113"/>
-          <a:ext cx="466725" cy="570905"/>
+          <a:off x="4595133" y="681378"/>
+          <a:ext cx="368753" cy="451064"/>
         </a:xfrm>
         <a:prstGeom prst="rect">
           <a:avLst/>
@@ -1244,10 +1244,10 @@
         <v>2</v>
       </c>
       <c r="B2" s="5" t="s">
+        <v>4</v>
+      </c>
+      <c r="C2" s="5" t="s">
         <v>3</v>
-      </c>
-      <c r="C2" s="5" t="s">
-        <v>4</v>
       </c>
       <c r="D2" s="5"/>
       <c r="E2" s="6" t="s">
